--- a/files/social_media_accounts.xlsx
+++ b/files/social_media_accounts.xlsx
@@ -11,7 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键人物账号" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平台覆盖统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'竞品官方账号总览'!$A$1:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'关键人物账号'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'平台覆盖统计'!$A$1:$M$18</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -545,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1309,27 +1313,27 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>Kimi Work</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>@n8n_io</t>
+          <t>@Kimi_Moonshot</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>n8n</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>r/n8n</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>@n8n.io (几乎无内容)</t>
+          <t>@kimiai.official</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1359,7 +1363,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Kimi智能助手 UID 3546607314274766</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1368,7 +1372,318 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>TRAE Work</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>MiniMax Code</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>@MiniMax__AI</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>MiniMax_稀宇极智 UID 3546878859807653</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Marvis</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Marvis马维斯 UID 3706967468018619</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>QClaw</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>腾讯电脑管家-管哥 团队账号 UID 626140785</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>阶跃 AI</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId2"/>
@@ -1426,10 +1741,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1441,7 +1752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1647,12 +1958,12 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Jan Oberhauser</t>
+          <t>Jeremy Chapman</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>Microsoft 365 Copilot</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1662,24 +1973,24 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>@JanOberhauser</t>
+          <t>@deployjeremy</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>https://x.com/JanOberhauser</t>
+          <t>https://x.com/deployjeremy</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>n8n 创始人/CEO (已不活跃)</t>
+          <t>Microsoft 365 首席演示官</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Jeremy Chapman</t>
+          <t>Mike Tholfsen</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1694,53 +2005,22 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>@deployjeremy</t>
+          <t>@mtholfsen</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>https://x.com/deployjeremy</t>
+          <t>https://x.com/mtholfsen</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Microsoft 365 首席演示官</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Mike Tholfsen</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Microsoft 365 Copilot</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>@mtholfsen</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>https://x.com/mtholfsen</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
           <t>Microsoft 365 教育行业负责人</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1752,12 +2032,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1769,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2572,7 +2848,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>Kimi Work</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -2582,12 +2858,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -2622,7 +2898,7 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
@@ -2631,10 +2907,336 @@
         </is>
       </c>
       <c r="M13" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>TRAE Work</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>MiniMax Code</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Marvis</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>QClaw</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>阶跃 AI</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>